--- a/product_selector_out/STM32F100 value Line - diff.xlsx
+++ b/product_selector_out/STM32F100 value Line - diff.xlsx
@@ -501,7 +501,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1216</v>
+        <v>1235</v>
       </c>
     </row>
     <row r="6">
@@ -521,7 +521,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="8">
@@ -611,7 +611,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1178</v>
+        <v>1197</v>
       </c>
     </row>
     <row r="18">
